--- a/content/page-related.xlsx
+++ b/content/page-related.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Japanese Aesthetics, Kakuzo Okakura, Kenkō, Change and impermanence, Nature and the universe, era-japan-from-the-heian-court-to-the-age-of-the-samurai</t>
+          <t>Japanese Aesthetics, Okakura Kakuzō, Kenkō, Change and impermanence, Nature and the universe, era-japan-from-the-heian-court-to-the-age-of-the-samurai</t>
         </is>
       </c>
     </row>
